--- a/NURBS IDX30 PYTHON ANALYSIS/Redo_front_4_24_26/15gps/3mps_analysis.xlsx
+++ b/NURBS IDX30 PYTHON ANALYSIS/Redo_front_4_24_26/15gps/3mps_analysis.xlsx
@@ -691,7 +691,7 @@
         <v>0</v>
       </c>
       <c r="W3">
-        <v>521.8283900179576</v>
+        <v>522.039204229432</v>
       </c>
       <c r="X3">
         <v>0.24840507</v>
@@ -869,7 +869,7 @@
         <v>0</v>
       </c>
       <c r="W5">
-        <v>24.208706581879</v>
+        <v>24.2080303550882</v>
       </c>
       <c r="X5">
         <v>0.248395224</v>
@@ -2245,7 +2245,7 @@
         <v>520.1823808969536</v>
       </c>
       <c r="V21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X21">
         <v>0.248244018</v>
@@ -2331,7 +2331,7 @@
         <v>518.1880232252869</v>
       </c>
       <c r="V22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X22">
         <v>0.248236712</v>
@@ -2417,7 +2417,7 @@
         <v>519.5254543185551</v>
       </c>
       <c r="V23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X23">
         <v>0.248229724</v>
